--- a/artfynd/A 43743-2024 artfynd.xlsx
+++ b/artfynd/A 43743-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79388153</v>
+        <v>79388154</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>796725.4215635308</v>
+        <v>796745</v>
       </c>
       <c r="R2" t="n">
-        <v>7231034.721891033</v>
+        <v>7231049</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,19 +743,9 @@
           <t>2019-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79388154</v>
+        <v>79388152</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,23 +783,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>796745.2406314213</v>
+        <v>796696</v>
       </c>
       <c r="R3" t="n">
-        <v>7231049.024610909</v>
+        <v>7231026</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,19 +836,9 @@
           <t>2019-08-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,6 +862,99 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>79388153</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Källbomark, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>796725</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7231035</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-08-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-08-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43743-2024 artfynd.xlsx
+++ b/artfynd/A 43743-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79388154</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -862,6 +872,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79388152</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -955,8 +970,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79388153</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>